--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756590</v>
+        <v>121756585</v>
       </c>
       <c r="B3" t="n">
-        <v>78705</v>
+        <v>96380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,26 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476995</v>
+        <v>476980</v>
       </c>
       <c r="R3" t="n">
-        <v>6593170</v>
+        <v>6593218</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756585</v>
+        <v>121756594</v>
       </c>
       <c r="B6" t="n">
-        <v>96380</v>
+        <v>74714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476980</v>
+        <v>477037</v>
       </c>
       <c r="R6" t="n">
-        <v>6593218</v>
+        <v>6593130</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756594</v>
+        <v>121756590</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>78705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477037</v>
+        <v>476995</v>
       </c>
       <c r="R7" t="n">
-        <v>6593130</v>
+        <v>6593170</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756585</v>
+        <v>121756573</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476980</v>
+        <v>477206</v>
       </c>
       <c r="R3" t="n">
-        <v>6593218</v>
+        <v>6593173</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756573</v>
+        <v>121756590</v>
       </c>
       <c r="B4" t="n">
-        <v>95660</v>
+        <v>78705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +911,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477206</v>
+        <v>476995</v>
       </c>
       <c r="R4" t="n">
-        <v>6593173</v>
+        <v>6593170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756594</v>
+        <v>121756585</v>
       </c>
       <c r="B6" t="n">
-        <v>74714</v>
+        <v>96380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1135,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477037</v>
+        <v>476980</v>
       </c>
       <c r="R6" t="n">
-        <v>6593130</v>
+        <v>6593218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756590</v>
+        <v>121756594</v>
       </c>
       <c r="B7" t="n">
-        <v>78705</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476995</v>
+        <v>477037</v>
       </c>
       <c r="R7" t="n">
-        <v>6593170</v>
+        <v>6593130</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756573</v>
+        <v>121756594</v>
       </c>
       <c r="B3" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +808,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477206</v>
+        <v>477037</v>
       </c>
       <c r="R3" t="n">
-        <v>6593173</v>
+        <v>6593130</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756590</v>
+        <v>121756585</v>
       </c>
       <c r="B4" t="n">
-        <v>78705</v>
+        <v>96380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,26 +914,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476995</v>
+        <v>476980</v>
       </c>
       <c r="R4" t="n">
-        <v>6593170</v>
+        <v>6593218</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756579</v>
+        <v>121756590</v>
       </c>
       <c r="B5" t="n">
-        <v>56561</v>
+        <v>78705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,54 +1017,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477036</v>
+        <v>476995</v>
       </c>
       <c r="R5" t="n">
-        <v>6593287</v>
+        <v>6593170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756585</v>
+        <v>121756573</v>
       </c>
       <c r="B6" t="n">
-        <v>96380</v>
+        <v>95660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476980</v>
+        <v>477206</v>
       </c>
       <c r="R6" t="n">
-        <v>6593218</v>
+        <v>6593173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756594</v>
+        <v>121756579</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>56561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,37 +1234,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477037</v>
+        <v>477036</v>
       </c>
       <c r="R7" t="n">
-        <v>6593130</v>
+        <v>6593287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,7 +1318,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756594</v>
+        <v>121756585</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
+        <v>96380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,30 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477037</v>
+        <v>476980</v>
       </c>
       <c r="R3" t="n">
-        <v>6593130</v>
+        <v>6593218</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756585</v>
+        <v>121756579</v>
       </c>
       <c r="B4" t="n">
-        <v>96380</v>
+        <v>56561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,42 +911,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476980</v>
+        <v>477036</v>
       </c>
       <c r="R4" t="n">
-        <v>6593218</v>
+        <v>6593287</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756590</v>
+        <v>121756594</v>
       </c>
       <c r="B5" t="n">
-        <v>78705</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476995</v>
+        <v>477037</v>
       </c>
       <c r="R5" t="n">
-        <v>6593170</v>
+        <v>6593130</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756573</v>
+        <v>121756590</v>
       </c>
       <c r="B6" t="n">
-        <v>95660</v>
+        <v>78705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1135,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477206</v>
+        <v>476995</v>
       </c>
       <c r="R6" t="n">
-        <v>6593173</v>
+        <v>6593170</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756579</v>
+        <v>121756573</v>
       </c>
       <c r="B7" t="n">
-        <v>56561</v>
+        <v>95660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,50 +1245,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477036</v>
+        <v>477206</v>
       </c>
       <c r="R7" t="n">
-        <v>6593287</v>
+        <v>6593173</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,6 +1317,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756594</v>
+        <v>121756573</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>95660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,26 +1033,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477037</v>
+        <v>477206</v>
       </c>
       <c r="R5" t="n">
-        <v>6593130</v>
+        <v>6593173</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1229,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756573</v>
+        <v>121756594</v>
       </c>
       <c r="B7" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,27 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477206</v>
+        <v>477037</v>
       </c>
       <c r="R7" t="n">
-        <v>6593173</v>
+        <v>6593130</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756585</v>
+        <v>121756573</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476980</v>
+        <v>477206</v>
       </c>
       <c r="R3" t="n">
-        <v>6593218</v>
+        <v>6593173</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756579</v>
+        <v>121756594</v>
       </c>
       <c r="B4" t="n">
-        <v>56561</v>
+        <v>74714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,50 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477036</v>
+        <v>477037</v>
       </c>
       <c r="R4" t="n">
-        <v>6593287</v>
+        <v>6593130</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,6 +986,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756573</v>
+        <v>121756590</v>
       </c>
       <c r="B5" t="n">
-        <v>95660</v>
+        <v>78705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,31 +1017,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477206</v>
+        <v>476995</v>
       </c>
       <c r="R5" t="n">
-        <v>6593173</v>
+        <v>6593170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756590</v>
+        <v>121756585</v>
       </c>
       <c r="B6" t="n">
-        <v>78705</v>
+        <v>96380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,26 +1127,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476995</v>
+        <v>476980</v>
       </c>
       <c r="R6" t="n">
-        <v>6593170</v>
+        <v>6593218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756594</v>
+        <v>121756579</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>56561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,37 +1234,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477037</v>
+        <v>477036</v>
       </c>
       <c r="R7" t="n">
-        <v>6593130</v>
+        <v>6593287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,7 +1318,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>121756573</v>
       </c>
       <c r="B3" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756594</v>
+        <v>121756585</v>
       </c>
       <c r="B4" t="n">
-        <v>74714</v>
+        <v>96398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,30 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477037</v>
+        <v>476980</v>
       </c>
       <c r="R4" t="n">
-        <v>6593130</v>
+        <v>6593218</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756590</v>
+        <v>121756594</v>
       </c>
       <c r="B5" t="n">
-        <v>78705</v>
+        <v>74727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476995</v>
+        <v>477037</v>
       </c>
       <c r="R5" t="n">
-        <v>6593170</v>
+        <v>6593130</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756585</v>
+        <v>121756590</v>
       </c>
       <c r="B6" t="n">
-        <v>96380</v>
+        <v>78718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,27 +1128,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476980</v>
+        <v>476995</v>
       </c>
       <c r="R6" t="n">
-        <v>6593218</v>
+        <v>6593170</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
         <v>121756579</v>
       </c>
       <c r="B7" t="n">
-        <v>56561</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756573</v>
+        <v>121756594</v>
       </c>
       <c r="B3" t="n">
-        <v>95678</v>
+        <v>74729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +808,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477206</v>
+        <v>477037</v>
       </c>
       <c r="R3" t="n">
-        <v>6593173</v>
+        <v>6593130</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756585</v>
+        <v>121756579</v>
       </c>
       <c r="B4" t="n">
-        <v>96398</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +910,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476980</v>
+        <v>477036</v>
       </c>
       <c r="R4" t="n">
-        <v>6593218</v>
+        <v>6593287</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +998,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756594</v>
+        <v>121756573</v>
       </c>
       <c r="B5" t="n">
-        <v>74727</v>
+        <v>95680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,26 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477037</v>
+        <v>477206</v>
       </c>
       <c r="R5" t="n">
-        <v>6593130</v>
+        <v>6593173</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1126,7 @@
         <v>121756590</v>
       </c>
       <c r="B6" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756579</v>
+        <v>121756585</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>96666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,54 +1241,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477036</v>
+        <v>476980</v>
       </c>
       <c r="R7" t="n">
-        <v>6593287</v>
+        <v>6593218</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,6 +1317,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756594</v>
+        <v>121756579</v>
       </c>
       <c r="B3" t="n">
-        <v>74729</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477037</v>
+        <v>477036</v>
       </c>
       <c r="R3" t="n">
-        <v>6593130</v>
+        <v>6593287</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +892,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756579</v>
+        <v>121756573</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>95687</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,50 +926,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477036</v>
+        <v>477206</v>
       </c>
       <c r="R4" t="n">
-        <v>6593287</v>
+        <v>6593173</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756573</v>
+        <v>121756590</v>
       </c>
       <c r="B5" t="n">
-        <v>95680</v>
+        <v>78721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1029,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477206</v>
+        <v>476995</v>
       </c>
       <c r="R5" t="n">
-        <v>6593173</v>
+        <v>6593170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756590</v>
+        <v>121756585</v>
       </c>
       <c r="B6" t="n">
-        <v>78720</v>
+        <v>96673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,26 +1139,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476995</v>
+        <v>476980</v>
       </c>
       <c r="R6" t="n">
-        <v>6593170</v>
+        <v>6593218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756585</v>
+        <v>121756594</v>
       </c>
       <c r="B7" t="n">
-        <v>96666</v>
+        <v>74729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,31 +1242,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476980</v>
+        <v>477037</v>
       </c>
       <c r="R7" t="n">
-        <v>6593218</v>
+        <v>6593130</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756579</v>
+        <v>121756590</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>78728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,54 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477036</v>
+        <v>476995</v>
       </c>
       <c r="R3" t="n">
-        <v>6593287</v>
+        <v>6593170</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756573</v>
+        <v>121756594</v>
       </c>
       <c r="B4" t="n">
-        <v>95687</v>
+        <v>74733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,27 +914,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477206</v>
+        <v>477037</v>
       </c>
       <c r="R4" t="n">
-        <v>6593173</v>
+        <v>6593130</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756590</v>
+        <v>121756573</v>
       </c>
       <c r="B5" t="n">
-        <v>78721</v>
+        <v>95696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,30 +1016,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476995</v>
+        <v>477206</v>
       </c>
       <c r="R5" t="n">
-        <v>6593170</v>
+        <v>6593173</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756585</v>
+        <v>121756579</v>
       </c>
       <c r="B6" t="n">
-        <v>96673</v>
+        <v>56573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,42 +1123,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476980</v>
+        <v>477036</v>
       </c>
       <c r="R6" t="n">
-        <v>6593218</v>
+        <v>6593287</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,7 +1211,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756594</v>
+        <v>121756585</v>
       </c>
       <c r="B7" t="n">
-        <v>74729</v>
+        <v>96682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,30 +1241,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477037</v>
+        <v>476980</v>
       </c>
       <c r="R7" t="n">
-        <v>6593130</v>
+        <v>6593218</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756590</v>
+        <v>121756594</v>
       </c>
       <c r="B3" t="n">
-        <v>78728</v>
+        <v>74737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476995</v>
+        <v>477037</v>
       </c>
       <c r="R3" t="n">
-        <v>6593170</v>
+        <v>6593130</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756594</v>
+        <v>121756590</v>
       </c>
       <c r="B4" t="n">
-        <v>74733</v>
+        <v>78732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477037</v>
+        <v>476995</v>
       </c>
       <c r="R4" t="n">
-        <v>6593130</v>
+        <v>6593170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756573</v>
+        <v>121756579</v>
       </c>
       <c r="B5" t="n">
-        <v>95696</v>
+        <v>56574</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1020,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477206</v>
+        <v>477036</v>
       </c>
       <c r="R5" t="n">
-        <v>6593173</v>
+        <v>6593287</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756579</v>
+        <v>121756573</v>
       </c>
       <c r="B6" t="n">
-        <v>56573</v>
+        <v>95704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,50 +1138,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477036</v>
+        <v>477206</v>
       </c>
       <c r="R6" t="n">
-        <v>6593287</v>
+        <v>6593173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,6 +1210,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>121756585</v>
       </c>
       <c r="B7" t="n">
-        <v>96682</v>
+        <v>96690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756594</v>
+        <v>121756573</v>
       </c>
       <c r="B3" t="n">
-        <v>74737</v>
+        <v>95706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,26 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477037</v>
+        <v>477206</v>
       </c>
       <c r="R3" t="n">
-        <v>6593130</v>
+        <v>6593173</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756590</v>
+        <v>121756585</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>96692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,26 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476995</v>
+        <v>476980</v>
       </c>
       <c r="R4" t="n">
-        <v>6593170</v>
+        <v>6593218</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756579</v>
+        <v>121756590</v>
       </c>
       <c r="B5" t="n">
-        <v>56574</v>
+        <v>78734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,54 +1018,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477036</v>
+        <v>476995</v>
       </c>
       <c r="R5" t="n">
-        <v>6593287</v>
+        <v>6593170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756573</v>
+        <v>121756579</v>
       </c>
       <c r="B6" t="n">
-        <v>95704</v>
+        <v>56576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,38 +1128,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477206</v>
+        <v>477036</v>
       </c>
       <c r="R6" t="n">
-        <v>6593173</v>
+        <v>6593287</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756585</v>
+        <v>121756594</v>
       </c>
       <c r="B7" t="n">
-        <v>96690</v>
+        <v>74739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,31 +1242,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476980</v>
+        <v>477037</v>
       </c>
       <c r="R7" t="n">
-        <v>6593218</v>
+        <v>6593130</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1334,6 +1334,242 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122767474</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56687</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476913</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6593217</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122776572</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477223</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6593215</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,6 +1783,446 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122853572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79380</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476990</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6593297</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122853621</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56680</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476911</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6593078</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122853601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90905</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>476918</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6593090</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122853633</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78851</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476887</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6593147</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815649</v>
+        <v>122815661</v>
       </c>
       <c r="B10" t="n">
-        <v>94758</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,31 +1584,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476987</v>
+        <v>477130</v>
       </c>
       <c r="R10" t="n">
-        <v>6593238</v>
+        <v>6593258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815661</v>
+        <v>122815649</v>
       </c>
       <c r="B11" t="n">
-        <v>79380</v>
+        <v>94766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,30 +1690,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477130</v>
+        <v>476987</v>
       </c>
       <c r="R11" t="n">
-        <v>6593258</v>
+        <v>6593238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853572</v>
+        <v>122853601</v>
       </c>
       <c r="B12" t="n">
-        <v>79380</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476990</v>
+        <v>476918</v>
       </c>
       <c r="R12" t="n">
-        <v>6593297</v>
+        <v>6593090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853621</v>
+        <v>122853572</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,54 +1907,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476911</v>
+        <v>476990</v>
       </c>
       <c r="R13" t="n">
-        <v>6593078</v>
+        <v>6593297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853601</v>
+        <v>122853633</v>
       </c>
       <c r="B14" t="n">
-        <v>90905</v>
+        <v>78855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2056,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476918</v>
+        <v>476887</v>
       </c>
       <c r="R14" t="n">
-        <v>6593090</v>
+        <v>6593147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853633</v>
+        <v>122853621</v>
       </c>
       <c r="B15" t="n">
-        <v>78851</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,41 +2115,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6450</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476887</v>
+        <v>476911</v>
       </c>
       <c r="R15" t="n">
-        <v>6593147</v>
+        <v>6593078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2207,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122767474</v>
+        <v>122776572</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,26 +1374,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476913</v>
+        <v>477223</v>
       </c>
       <c r="R8" t="n">
-        <v>6593217</v>
+        <v>6593215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,19 +1417,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776572</v>
+        <v>122767474</v>
       </c>
       <c r="B9" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,25 +1458,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,20 +1484,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477223</v>
+        <v>476913</v>
       </c>
       <c r="R9" t="n">
-        <v>6593215</v>
+        <v>6593217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,9 +1533,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853572</v>
+        <v>122853633</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>78855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,25 +1903,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476990</v>
+        <v>476887</v>
       </c>
       <c r="R13" t="n">
-        <v>6593297</v>
+        <v>6593147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853633</v>
+        <v>122853572</v>
       </c>
       <c r="B14" t="n">
-        <v>78855</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,25 +2009,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476887</v>
+        <v>476990</v>
       </c>
       <c r="R14" t="n">
-        <v>6593147</v>
+        <v>6593297</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1681,7 +1681,7 @@
         <v>122815649</v>
       </c>
       <c r="B11" t="n">
-        <v>94766</v>
+        <v>94768</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853633</v>
+        <v>122853621</v>
       </c>
       <c r="B13" t="n">
-        <v>78855</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,41 +1903,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476887</v>
+        <v>476911</v>
       </c>
       <c r="R13" t="n">
-        <v>6593147</v>
+        <v>6593078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2103,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853621</v>
+        <v>122853633</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>78855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,58 +2131,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476911</v>
+        <v>476887</v>
       </c>
       <c r="R15" t="n">
-        <v>6593078</v>
+        <v>6593147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,6 +2206,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,6 +2223,118 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122931684</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476987</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6593238</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122776572</v>
+        <v>122767474</v>
       </c>
       <c r="B8" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,20 +1374,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477223</v>
+        <v>476913</v>
       </c>
       <c r="R8" t="n">
-        <v>6593215</v>
+        <v>6593217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,9 +1423,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122767474</v>
+        <v>122776572</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,25 +1474,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,26 +1500,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476913</v>
+        <v>477223</v>
       </c>
       <c r="R9" t="n">
-        <v>6593217</v>
+        <v>6593215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,19 +1543,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815661</v>
+        <v>122815649</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>94768</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,30 +1584,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1615,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477130</v>
+        <v>476987</v>
       </c>
       <c r="R10" t="n">
-        <v>6593258</v>
+        <v>6593238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815649</v>
+        <v>122815661</v>
       </c>
       <c r="B11" t="n">
-        <v>94768</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,31 +1691,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476987</v>
+        <v>477130</v>
       </c>
       <c r="R11" t="n">
-        <v>6593238</v>
+        <v>6593258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853621</v>
+        <v>122853572</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,54 +1907,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476911</v>
+        <v>476990</v>
       </c>
       <c r="R13" t="n">
-        <v>6593078</v>
+        <v>6593297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853572</v>
+        <v>122853633</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>78855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,25 +2009,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2056,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476990</v>
+        <v>476887</v>
       </c>
       <c r="R14" t="n">
-        <v>6593297</v>
+        <v>6593147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853633</v>
+        <v>122853621</v>
       </c>
       <c r="B15" t="n">
-        <v>78855</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,41 +2115,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6450</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476887</v>
+        <v>476911</v>
       </c>
       <c r="R15" t="n">
-        <v>6593147</v>
+        <v>6593078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2207,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122767474</v>
+        <v>122776572</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,26 +1374,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476913</v>
+        <v>477223</v>
       </c>
       <c r="R8" t="n">
-        <v>6593217</v>
+        <v>6593215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,19 +1417,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776572</v>
+        <v>122767474</v>
       </c>
       <c r="B9" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,25 +1458,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,20 +1484,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477223</v>
+        <v>476913</v>
       </c>
       <c r="R9" t="n">
-        <v>6593215</v>
+        <v>6593217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,9 +1533,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>122815649</v>
       </c>
       <c r="B10" t="n">
-        <v>94768</v>
+        <v>94776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853601</v>
+        <v>122853633</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>78855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476918</v>
+        <v>476887</v>
       </c>
       <c r="R12" t="n">
-        <v>6593090</v>
+        <v>6593147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853633</v>
+        <v>122853601</v>
       </c>
       <c r="B14" t="n">
-        <v>78855</v>
+        <v>90917</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476887</v>
+        <v>476918</v>
       </c>
       <c r="R14" t="n">
-        <v>6593147</v>
+        <v>6593090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>122853633</v>
       </c>
       <c r="B12" t="n">
-        <v>78855</v>
+        <v>78852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853572</v>
+        <v>122853621</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,37 +1907,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476990</v>
+        <v>476911</v>
       </c>
       <c r="R13" t="n">
-        <v>6593297</v>
+        <v>6593078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853601</v>
+        <v>122853572</v>
       </c>
       <c r="B14" t="n">
-        <v>90917</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,25 +2025,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476918</v>
+        <v>476990</v>
       </c>
       <c r="R14" t="n">
-        <v>6593090</v>
+        <v>6593297</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853621</v>
+        <v>122853601</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>90917</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,58 +2131,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476911</v>
+        <v>476918</v>
       </c>
       <c r="R15" t="n">
-        <v>6593078</v>
+        <v>6593090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,6 +2206,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815649</v>
+        <v>122815661</v>
       </c>
       <c r="B10" t="n">
-        <v>94776</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,31 +1584,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476987</v>
+        <v>477130</v>
       </c>
       <c r="R10" t="n">
-        <v>6593238</v>
+        <v>6593258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815661</v>
+        <v>122815649</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>94776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,30 +1690,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477130</v>
+        <v>476987</v>
       </c>
       <c r="R11" t="n">
-        <v>6593258</v>
+        <v>6593238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853633</v>
+        <v>122853601</v>
       </c>
       <c r="B12" t="n">
-        <v>78852</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476887</v>
+        <v>476918</v>
       </c>
       <c r="R12" t="n">
-        <v>6593147</v>
+        <v>6593090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853621</v>
+        <v>122853572</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,54 +1907,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476911</v>
+        <v>476990</v>
       </c>
       <c r="R13" t="n">
-        <v>6593078</v>
+        <v>6593297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853572</v>
+        <v>122853621</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,37 +2013,54 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476990</v>
+        <v>476911</v>
       </c>
       <c r="R14" t="n">
-        <v>6593297</v>
+        <v>6593078</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2101,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853601</v>
+        <v>122853633</v>
       </c>
       <c r="B15" t="n">
-        <v>90917</v>
+        <v>78852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476918</v>
+        <v>476887</v>
       </c>
       <c r="R15" t="n">
-        <v>6593090</v>
+        <v>6593147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815661</v>
+        <v>122815649</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>94776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,30 +1584,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1615,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477130</v>
+        <v>476987</v>
       </c>
       <c r="R10" t="n">
-        <v>6593258</v>
+        <v>6593238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815649</v>
+        <v>122815661</v>
       </c>
       <c r="B11" t="n">
-        <v>94776</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,31 +1691,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476987</v>
+        <v>477130</v>
       </c>
       <c r="R11" t="n">
-        <v>6593238</v>
+        <v>6593258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853601</v>
+        <v>122853572</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476918</v>
+        <v>476990</v>
       </c>
       <c r="R12" t="n">
-        <v>6593090</v>
+        <v>6593297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853572</v>
+        <v>122853621</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,37 +1907,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476990</v>
+        <v>476911</v>
       </c>
       <c r="R13" t="n">
-        <v>6593297</v>
+        <v>6593078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853621</v>
+        <v>122853633</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>78852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,58 +2025,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476911</v>
+        <v>476887</v>
       </c>
       <c r="R14" t="n">
-        <v>6593078</v>
+        <v>6593147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,6 +2100,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853633</v>
+        <v>122853601</v>
       </c>
       <c r="B15" t="n">
-        <v>78852</v>
+        <v>90917</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476887</v>
+        <v>476918</v>
       </c>
       <c r="R15" t="n">
-        <v>6593147</v>
+        <v>6593090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122776572</v>
+        <v>122767474</v>
       </c>
       <c r="B8" t="n">
-        <v>56680</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,20 +1374,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477223</v>
+        <v>476913</v>
       </c>
       <c r="R8" t="n">
-        <v>6593215</v>
+        <v>6593217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,9 +1423,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122767474</v>
+        <v>122776572</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>56683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,25 +1474,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,26 +1500,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476913</v>
+        <v>477223</v>
       </c>
       <c r="R9" t="n">
-        <v>6593217</v>
+        <v>6593215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,19 +1543,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>122815649</v>
       </c>
       <c r="B10" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>122815661</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853572</v>
+        <v>122853601</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>90920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476990</v>
+        <v>476918</v>
       </c>
       <c r="R12" t="n">
-        <v>6593297</v>
+        <v>6593090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853621</v>
+        <v>122853633</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>78855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,58 +1903,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476911</v>
+        <v>476887</v>
       </c>
       <c r="R13" t="n">
-        <v>6593078</v>
+        <v>6593147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853633</v>
+        <v>122853621</v>
       </c>
       <c r="B14" t="n">
-        <v>78852</v>
+        <v>56683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,41 +2009,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6450</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476887</v>
+        <v>476911</v>
       </c>
       <c r="R14" t="n">
-        <v>6593147</v>
+        <v>6593078</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2101,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853601</v>
+        <v>122853572</v>
       </c>
       <c r="B15" t="n">
-        <v>90917</v>
+        <v>79387</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476918</v>
+        <v>476990</v>
       </c>
       <c r="R15" t="n">
-        <v>6593090</v>
+        <v>6593297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
         <v>122931684</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122767474</v>
+        <v>122776572</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>56683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,26 +1374,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476913</v>
+        <v>477223</v>
       </c>
       <c r="R8" t="n">
-        <v>6593217</v>
+        <v>6593215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,19 +1417,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776572</v>
+        <v>122767474</v>
       </c>
       <c r="B9" t="n">
-        <v>56683</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,25 +1458,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,20 +1484,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Märrsprängardrågen, Märrsprängardrågen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477223</v>
+        <v>476913</v>
       </c>
       <c r="R9" t="n">
-        <v>6593215</v>
+        <v>6593217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,9 +1533,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>122815649</v>
       </c>
       <c r="B10" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>122815661</v>
       </c>
       <c r="B11" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853601</v>
+        <v>122853633</v>
       </c>
       <c r="B12" t="n">
-        <v>90920</v>
+        <v>78857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476918</v>
+        <v>476887</v>
       </c>
       <c r="R12" t="n">
-        <v>6593090</v>
+        <v>6593147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853633</v>
+        <v>122853601</v>
       </c>
       <c r="B13" t="n">
-        <v>78855</v>
+        <v>90922</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476887</v>
+        <v>476918</v>
       </c>
       <c r="R13" t="n">
-        <v>6593147</v>
+        <v>6593090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122853621</v>
+        <v>122853572</v>
       </c>
       <c r="B14" t="n">
-        <v>56683</v>
+        <v>79389</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,54 +2013,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476911</v>
+        <v>476990</v>
       </c>
       <c r="R14" t="n">
-        <v>6593078</v>
+        <v>6593297</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,6 +2084,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853572</v>
+        <v>122853621</v>
       </c>
       <c r="B15" t="n">
-        <v>79387</v>
+        <v>56683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,37 +2119,54 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476990</v>
+        <v>476911</v>
       </c>
       <c r="R15" t="n">
-        <v>6593297</v>
+        <v>6593078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2207,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>122931684</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122815649</v>
+        <v>122815661</v>
       </c>
       <c r="B10" t="n">
-        <v>94781</v>
+        <v>79390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,31 +1584,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476987</v>
+        <v>477130</v>
       </c>
       <c r="R10" t="n">
-        <v>6593238</v>
+        <v>6593258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122815661</v>
+        <v>122815649</v>
       </c>
       <c r="B11" t="n">
-        <v>79389</v>
+        <v>94787</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,30 +1690,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477130</v>
+        <v>476987</v>
       </c>
       <c r="R11" t="n">
-        <v>6593258</v>
+        <v>6593238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122853633</v>
+        <v>122853601</v>
       </c>
       <c r="B12" t="n">
-        <v>78857</v>
+        <v>90928</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476887</v>
+        <v>476918</v>
       </c>
       <c r="R12" t="n">
-        <v>6593147</v>
+        <v>6593090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122853601</v>
+        <v>122853621</v>
       </c>
       <c r="B13" t="n">
-        <v>90922</v>
+        <v>56683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,41 +1903,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476918</v>
+        <v>476911</v>
       </c>
       <c r="R13" t="n">
-        <v>6593090</v>
+        <v>6593078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>122853572</v>
       </c>
       <c r="B14" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122853621</v>
+        <v>122853633</v>
       </c>
       <c r="B15" t="n">
-        <v>56683</v>
+        <v>78858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,58 +2131,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476911</v>
+        <v>476887</v>
       </c>
       <c r="R15" t="n">
-        <v>6593078</v>
+        <v>6593147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,6 +2206,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>122931684</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>122931684</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,253 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128375376</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477190</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6593177</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128371445</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477047</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6593240</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,6 +2581,342 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128479867</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477182</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6593103</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128480350</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98512</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477182</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6593103</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överståndare.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128479819</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>477154</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6593095</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98398</v>
+        <v>98491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>128479819</v>
       </c>
       <c r="B21" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98605</v>
+        <v>98613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>128479819</v>
       </c>
       <c r="B21" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>128479819</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>128479819</v>
       </c>
       <c r="B21" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -2340,7 +2340,7 @@
         <v>128375376</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128371445</v>
       </c>
       <c r="B18" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128479867</v>
       </c>
       <c r="B19" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128480350</v>
       </c>
       <c r="B20" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>128479819</v>
       </c>
       <c r="B21" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58022-2020 artfynd.xlsx
+++ b/artfynd/A 58022-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2918,6 +2918,107 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129529874</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477182</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6593224</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
